--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M115"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4846.3</v>
+        <v>4901.41</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3514.79</v>
+        <v>3529.36</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5727.51</v>
+        <v>5770.89</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4604.81</v>
+        <v>4622.26</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>33708.48</v>
+        <v>33623.37</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>15161.52</v>
+        <v>15123.24</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6778.31</v>
+        <v>6761.2</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>56594.6</v>
+        <v>56451.71</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>28423.04</v>
+        <v>28351.28</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5053.04</v>
+        <v>5040.29</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7516.73</v>
+        <v>7497.75</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>77321.11</v>
+        <v>77145.61</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6363.37</v>
+        <v>6347.65</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7213.25</v>
+        <v>7195.44</v>
       </c>
     </row>
     <row r="16">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2069-4231-CM26</t>
+          <t>2069-4233-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2069-4233-CM26</t>
+          <t>2069-4231-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3606.63</v>
+        <v>3624.34</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3635.44</v>
+        <v>3653.3</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10445.75</v>
+        <v>10497.06</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>75767.67999999999</v>
+        <v>76139.87</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4319.14</v>
+        <v>4333.46</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>24002.62</v>
+        <v>24082.25</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>46850.45</v>
+        <v>46999.57</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>36227.15</v>
+        <v>36342.45</v>
       </c>
     </row>
     <row r="29">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2673.58</v>
+        <v>2687.79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>812030-622-CM26</t>
+          <t>3378-4788-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2976.3</v>
+        <v>63871.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3378-4788-CM26</t>
+          <t>812030-622-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>63228.9</v>
+        <v>3006.57</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2939.43</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6437.49</v>
+        <v>6388.66</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4149.17</v>
+        <v>4079.07</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2648.4</v>
+        <v>2603.65</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4947.48</v>
+        <v>4863.89</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>30463.28</v>
+        <v>30044.7</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2765.89</v>
+        <v>2727.89</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4291.66</v>
+        <v>4232.69</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2660.88</v>
+        <v>2624.32</v>
       </c>
     </row>
     <row r="41">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5637.91</v>
+        <v>5602.96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>812030-677-CM26</t>
+          <t>1947-2902-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.004-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7943.6</v>
+        <v>2566.82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1947-2902-CM26</t>
+          <t>812030-677-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.608.004-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2529.16</v>
+        <v>8061.89</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3328-1426-CM26</t>
+          <t>1057501-5644-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3215.03</v>
+        <v>2673.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057501-5644-CM26</t>
+          <t>3328-1426-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2634.54</v>
+        <v>3262.91</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3913.16</v>
+        <v>3940.18</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4081.66</v>
+        <v>4094.28</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>68958.37</v>
+        <v>68775.98</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>15065.08</v>
+        <v>15025.23</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>56234.6</v>
+        <v>56085.87</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>14643.02</v>
+        <v>14604.29</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>28242.24</v>
+        <v>28167.55</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4550.58</v>
+        <v>4489.96</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>16741.53</v>
+        <v>16518.53</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6291.28</v>
+        <v>6207.48</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4185.38</v>
+        <v>4129.63</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3806.96</v>
+        <v>3732.44</v>
       </c>
     </row>
     <row r="58">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>74521.42999999999</v>
+        <v>73062.75999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>812030-712-CM26</t>
+          <t>2111-10165-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>46288.97</v>
+        <v>4457.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057489-8114-CM26</t>
+          <t>2111-10164-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5254.47</v>
+        <v>4288.39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2111-10164-CM26</t>
+          <t>1057489-8114-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4133,17 +4133,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4378.38</v>
+        <v>5146.48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2111-10165-CM26</t>
+          <t>812030-712-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4550.58</v>
+        <v>45337.65</v>
       </c>
     </row>
     <row r="63">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3533.06</v>
+        <v>3566.62</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2069-5934-CM26</t>
+          <t>2069-5517-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3670.59</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2069-5911-CM26</t>
+          <t>2069-5522-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5250.21</v>
+        <v>3784.76</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2069-5908-CM26</t>
+          <t>2069-5525-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>12723.89</v>
+        <v>3513.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2069-5528-CM26</t>
+          <t>2069-5526-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5437.12</v>
+        <v>2346.16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2069-5912-CM26</t>
+          <t>2069-5528-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3477.5</v>
+        <v>5458.34</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2069-5525-CM26</t>
+          <t>2069-5908-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3500.14</v>
+        <v>12773.56</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2069-5522-CM26</t>
+          <t>2069-5911-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3770.04</v>
+        <v>5270.71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2069-5526-CM26</t>
+          <t>2069-5912-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2337.04</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2069-5517-CM26</t>
+          <t>2069-5934-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3477.5</v>
+        <v>3684.92</v>
       </c>
     </row>
     <row r="73">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4061.36</v>
+        <v>4102.21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2069-5521-CM26</t>
+          <t>2069-6030-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>8011.34</v>
+        <v>7414.69</v>
       </c>
     </row>
     <row r="75">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3298.79</v>
+        <v>3331.82</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2069-6030-CM26</t>
+          <t>2069-5521-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7341.18</v>
+        <v>8091.56</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>10411.24</v>
+        <v>10464.29</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>6710.74</v>
+        <v>6736.87</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8724.41</v>
+        <v>8758.370000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>24313.46</v>
+        <v>24408.11</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>11949.35</v>
+        <v>11974.81</v>
       </c>
     </row>
     <row r="82">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>67215.66</v>
+        <v>67653.86</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3378-6046-CM26</t>
+          <t>2069-6189-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4061.36</v>
+        <v>10863.72</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2069-6356-CM26</t>
+          <t>2069-6191-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>13195.15</v>
+        <v>7561.02</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2069-6352-CM26</t>
+          <t>1057503-3428-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5597,17 +5597,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4075.79</v>
+        <v>42919.12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2069-6191-CM26</t>
+          <t>2069-6352-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7543.72</v>
+        <v>4085.13</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2069-6189-CM26</t>
+          <t>2069-6356-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>10838.87</v>
+        <v>13225.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1057503-3428-CM26</t>
+          <t>3378-6046-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5780,17 +5780,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>42820.93</v>
+        <v>4070.68</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1057503-3492-CM26</t>
+          <t>1057501-7822-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>14717.83</v>
+        <v>4117.74</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057501-7822-CM26</t>
+          <t>1057503-3492-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4090.36</v>
+        <v>14816.35</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>17447.93</v>
+        <v>17570.04</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2683.93</v>
+        <v>2702.72</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4177.28</v>
+        <v>4206.51</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>11949.35</v>
+        <v>12032.97</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>73626.42999999999</v>
+        <v>73393.87</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4415.74</v>
+        <v>4406.13</v>
       </c>
     </row>
     <row r="97">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5460.62</v>
+        <v>5448.74</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057501-7870-CM26</t>
+          <t>1057501-7867-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>55328.92</v>
+        <v>57603.57</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1057501-8128-CM26</t>
+          <t>1057501-7870-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>20785.19</v>
+        <v>55218.01</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>812030-765-CM26</t>
+          <t>1057501-7871-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10411.24</v>
+        <v>27708.12</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1057501-7867-CM26</t>
+          <t>812030-765-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6573,17 +6573,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>57719.28</v>
+        <v>10390.37</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1057501-7871-CM26</t>
+          <t>1057501-8128-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>27763.77</v>
+        <v>20743.53</v>
       </c>
     </row>
     <row r="103">
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2684.3</v>
+        <v>2640.98</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3328-1738-CM26</t>
+          <t>3378-6339-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6756,17 +6756,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>5648.29</v>
+        <v>2461.82</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1549-3226-CM26</t>
+          <t>3328-1738-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>69079.46000000001</v>
+        <v>5557.72</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3378-6339-CM26</t>
+          <t>1549-3226-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2501.94</v>
+        <v>67971.87</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2770.58</v>
+        <v>2738.34</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3521.8</v>
+        <v>3502.27</v>
       </c>
     </row>
     <row r="109">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>45617.07</v>
+        <v>45364.17</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1057501-8311-CM26</t>
+          <t>2069-6712-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>6022.45</v>
+        <v>5335.07</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2069-6759-CM26</t>
+          <t>2069-6748-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3298.79</v>
+        <v>3500.77</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1549-3347-CM26</t>
+          <t>2069-6759-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>49391.07</v>
+        <v>3320.87</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2069-6712-CM26</t>
+          <t>1057501-8311-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5299.59</v>
+        <v>6062.76</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2069-6748-CM26</t>
+          <t>1549-3347-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3477.5</v>
+        <v>49721.66</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,312 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>20124.56</v>
+        <v>20259.26</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1057489-9198-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>61.608.406-2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>3845.24</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1057489-9314-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>61.608.406-2</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>61473.81</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1057491-4650-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>61.608.408-9</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>NEUMANN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>78.936.310-2</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>12173.07</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1057049-17460-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>BLUNDING S.A.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>11343.41</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1549-3804-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>9764.559999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metropolitana" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metropolitana" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -758,7 +758,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1549-2076-CM26</t>
+          <t>1549-2085-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>33623.37</v>
+        <v>5040.29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1549-2077-CM26</t>
+          <t>1549-2082-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>15123.24</v>
+        <v>28351.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1549-2080-CM26</t>
+          <t>1549-2081-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6761.2</v>
+        <v>56451.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1549-2081-CM26</t>
+          <t>3471-1634-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,17 +961,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>60.505.723-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>Carabineros de Chile - Hospital de Carabineros</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>56451.71</v>
+        <v>7497.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1549-2082-CM26</t>
+          <t>1549-2077-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>28351.28</v>
+        <v>15123.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1549-2085-CM26</t>
+          <t>1549-2076-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5040.29</v>
+        <v>33623.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3471-1634-CM26</t>
+          <t>1549-2080-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.505.723-3</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7497.75</v>
+        <v>6761.2</v>
       </c>
     </row>
     <row r="13">
@@ -1246,7 +1246,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3378-4411-CM26</t>
+          <t>2069-4170-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6347.65</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2069-4326-CM26</t>
+          <t>2069-4231-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7195.44</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2069-4280-CM26</t>
+          <t>2069-4233-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2069-4233-CM26</t>
+          <t>2069-4234-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2069-4231-CM26</t>
+          <t>2069-4280-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2069-4170-CM26</t>
+          <t>2069-4326-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3597.72</v>
+        <v>7195.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2069-4234-CM26</t>
+          <t>3378-4411-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3597.72</v>
+        <v>6347.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2069-4325-CM26</t>
+          <t>2069-4731-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3624.34</v>
+        <v>76139.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2069-4512-CM26</t>
+          <t>3328-1262-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3653.3</v>
+        <v>10497.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3328-1262-CM26</t>
+          <t>2069-4325-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10497.06</v>
+        <v>3624.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2069-4731-CM26</t>
+          <t>2069-4512-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>76139.87</v>
+        <v>3653.3</v>
       </c>
     </row>
     <row r="25">
@@ -2222,7 +2222,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3378-4788-CM26</t>
+          <t>812030-622-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>63871.9</v>
+        <v>3006.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>812030-622-CM26</t>
+          <t>3378-4788-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3006.57</v>
+        <v>63871.9</v>
       </c>
     </row>
     <row r="32">
@@ -2649,7 +2649,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057503-3007-CM26</t>
+          <t>3328-1444-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2669,17 +2669,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>30044.7</v>
+        <v>2727.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3328-1444-CM26</t>
+          <t>812030-659-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,17 +2730,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2727.89</v>
+        <v>4232.69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>812030-659-CM26</t>
+          <t>1057503-3007-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4232.69</v>
+        <v>30044.7</v>
       </c>
     </row>
     <row r="40">
@@ -2954,7 +2954,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1947-2902-CM26</t>
+          <t>1057501-5644-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.608.004-0</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2566.82</v>
+        <v>2673.77</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>812030-677-CM26</t>
+          <t>3328-1426-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>8061.89</v>
+        <v>3262.91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057501-5644-CM26</t>
+          <t>1947-2902-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.004-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2673.77</v>
+        <v>2566.82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3328-1426-CM26</t>
+          <t>812030-677-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3262.91</v>
+        <v>8061.89</v>
       </c>
     </row>
     <row r="46">
@@ -3320,7 +3320,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1549-2697-CM26</t>
+          <t>1549-2709-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>68775.98</v>
+        <v>28167.55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1549-2703-CM26</t>
+          <t>1549-2707-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>15025.23</v>
+        <v>14604.29</v>
       </c>
     </row>
     <row r="50">
@@ -3503,7 +3503,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1549-2707-CM26</t>
+          <t>1549-2703-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>14604.29</v>
+        <v>15025.23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1549-2709-CM26</t>
+          <t>1549-2697-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>28167.55</v>
+        <v>68775.98</v>
       </c>
     </row>
     <row r="53">
@@ -3869,7 +3869,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3328-1516-CM26</t>
+          <t>812030-613-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3732.44</v>
+        <v>73062.75999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>812030-613-CM26</t>
+          <t>3328-1516-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>73062.75999999999</v>
+        <v>3732.44</v>
       </c>
     </row>
     <row r="59">
@@ -4113,7 +4113,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057489-8114-CM26</t>
+          <t>812030-712-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5146.48</v>
+        <v>45337.65</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>812030-712-CM26</t>
+          <t>1057489-8114-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>45337.65</v>
+        <v>5146.48</v>
       </c>
     </row>
     <row r="63">
@@ -4296,7 +4296,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2069-5517-CM26</t>
+          <t>2069-5912-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4357,7 +4357,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2069-5522-CM26</t>
+          <t>2069-5934-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3784.76</v>
+        <v>3684.92</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2069-5525-CM26</t>
+          <t>2069-5911-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3513.8</v>
+        <v>5270.71</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2069-5526-CM26</t>
+          <t>2069-5528-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2346.16</v>
+        <v>5458.34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2069-5528-CM26</t>
+          <t>2069-5908-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5458.34</v>
+        <v>12773.56</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2069-5908-CM26</t>
+          <t>2069-5525-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>12773.56</v>
+        <v>3513.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2069-5911-CM26</t>
+          <t>2069-5522-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5270.71</v>
+        <v>3784.76</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2069-5912-CM26</t>
+          <t>2069-5517-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4784,7 +4784,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2069-5934-CM26</t>
+          <t>2069-5526-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3684.92</v>
+        <v>2346.16</v>
       </c>
     </row>
     <row r="73">
@@ -4906,7 +4906,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2069-6030-CM26</t>
+          <t>2069-5521-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>7414.69</v>
+        <v>8091.56</v>
       </c>
     </row>
     <row r="75">
@@ -5028,7 +5028,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2069-5521-CM26</t>
+          <t>2069-6030-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8091.56</v>
+        <v>7414.69</v>
       </c>
     </row>
     <row r="77">
@@ -5150,7 +5150,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1057049-15556-CM26</t>
+          <t>2069-5913-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>6736.87</v>
+        <v>8758.370000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2069-5913-CM26</t>
+          <t>1057489-8316-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8758.370000000001</v>
+        <v>24408.11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1057489-8316-CM26</t>
+          <t>1057049-15556-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5292,17 +5292,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>24408.11</v>
+        <v>6736.87</v>
       </c>
     </row>
     <row r="81">
@@ -5821,7 +5821,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1057501-7822-CM26</t>
+          <t>1057503-3492-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4117.74</v>
+        <v>14816.35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057503-3492-CM26</t>
+          <t>1057501-7822-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>14816.35</v>
+        <v>4117.74</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1057882-9-CM26</t>
+          <t>1057491-4167-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>17570.04</v>
+        <v>12032.97</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3378-6087-CM26</t>
+          <t>812030-753-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2702.72</v>
+        <v>4206.51</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>812030-753-CM26</t>
+          <t>3378-6087-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4206.51</v>
+        <v>2702.72</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057491-4167-CM26</t>
+          <t>1057882-9-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>12032.97</v>
+        <v>17570.04</v>
       </c>
     </row>
     <row r="95">
@@ -6736,7 +6736,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3378-6339-CM26</t>
+          <t>3328-1738-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6756,17 +6756,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2461.82</v>
+        <v>5557.72</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3328-1738-CM26</t>
+          <t>1549-3226-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>5557.72</v>
+        <v>67971.87</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1549-3226-CM26</t>
+          <t>3378-6339-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>67971.87</v>
+        <v>2461.82</v>
       </c>
     </row>
     <row r="107">
@@ -7102,7 +7102,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2069-6712-CM26</t>
+          <t>3328-1937-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5335.07</v>
+        <v>20259.26</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2069-6748-CM26</t>
+          <t>1549-3347-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3500.77</v>
+        <v>49721.66</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2069-6759-CM26</t>
+          <t>1057501-8311-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3320.87</v>
+        <v>6062.76</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1057501-8311-CM26</t>
+          <t>2069-6748-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6062.76</v>
+        <v>3500.77</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1549-3347-CM26</t>
+          <t>2069-6712-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>49721.66</v>
+        <v>5335.07</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3328-1937-CM26</t>
+          <t>2069-6759-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>20259.26</v>
+        <v>3320.87</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1057489-9198-CM26</t>
+          <t>1057049-17118-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3845.24</v>
+        <v>2883.93</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1057489-9314-CM26</t>
+          <t>1057489-9198-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>61473.81</v>
+        <v>3845.24</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1057491-4650-CM26</t>
+          <t>1057049-17208-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,22 +7605,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>12173.07</v>
+        <v>66844.28999999999</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1057049-17460-CM26</t>
+          <t>1057494-2969-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.102-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
+          <t>77.535.386-4</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>11343.41</v>
+        <v>3294.09</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1549-3804-CM26</t>
+          <t>800-4708-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7767,7 +7767,2630 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
+        <v>3785.73</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1057489-9314-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>61.608.406-2</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>61473.81</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1057491-4650-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>61.608.408-9</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>NEUMANN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>78.936.310-2</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>12173.07</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2069-6962-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>5313.91</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2069-6762-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>5250.87</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2069-6959-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>9601.57</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2069-6703-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>7478.62</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2069-6964-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>5446.38</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1057501-8921-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>5742.68</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>812030-804-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>7690.35</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>812030-824-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>10599.79</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1057491-4687-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>61.608.408-9</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>NEUMANN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>78.936.310-2</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>6082.87</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>3378-6928-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>61.101.030-3</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>4145.84</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1549-3603-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>68447.7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2069-7311-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>8498.540000000001</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1549-3602-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>73577.87</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2111-11638-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>ARENYS MED S.A.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>4100.35</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2111-11646-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>ARENYS MED S.A.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>2603.4</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1057049-17460-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>BLUNDING S.A.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>11343.41</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2069-7593-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>19069.59</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2069-7595-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>14853.23</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2069-7602-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>7578.59</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1057501-9565-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>46134.59</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>812030-890-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>3722.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1549-3689-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>56556.75</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2111-11754-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>2621.92</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>812030-798-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>5757.16</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1641-19026-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>61.608.204-3</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>HEMISFERIO SUR S.A.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>7581.93</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1641-19028-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>61.608.204-3</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>HEMISFERIO SUR S.A.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>4717.64</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1057049-17479-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>3732.64</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>3328-2156-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>61.103.007-K</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>14161.61</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>3378-7297-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>61.101.030-3</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>3912.08</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1057049-17540-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Medyssey</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>2358.69</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1947-3865-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>61.608.004-0</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>2498.03</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>812030-895-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>59644.5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>3378-7368-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>61.101.030-3</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>3608.81</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>3328-2217-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>61.103.007-K</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>2779.07</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>3328-2227-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>61.103.007-K</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>AETICA SPA</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>8138.68</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1549-3801-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>69228.87</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1549-3800-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>75746.94</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>3328-2237-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>61.103.007-K</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>3504.09</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1549-3804-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
         <v>9764.559999999999</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1549-3803-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>55550.71</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2109-1794-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>61.608.203-5</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>7492.09</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1549-2085-CM26</t>
+          <t>1549-2076-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5040.29</v>
+        <v>33623.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1549-2082-CM26</t>
+          <t>1549-2077-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>28351.28</v>
+        <v>15123.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1549-2081-CM26</t>
+          <t>1549-2080-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>56451.71</v>
+        <v>6761.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3471-1634-CM26</t>
+          <t>1549-2081-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,17 +961,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.505.723-3</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7497.75</v>
+        <v>56451.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1549-2077-CM26</t>
+          <t>1549-2082-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>15123.24</v>
+        <v>28351.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1549-2076-CM26</t>
+          <t>1549-2085-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>33623.37</v>
+        <v>5040.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1549-2080-CM26</t>
+          <t>3471-1634-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>60.505.723-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6761.2</v>
+        <v>7497.75</v>
       </c>
     </row>
     <row r="13">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2069-4731-CM26</t>
+          <t>2069-4325-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>76139.87</v>
+        <v>3624.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3328-1262-CM26</t>
+          <t>2069-4512-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>10497.06</v>
+        <v>3653.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2069-4325-CM26</t>
+          <t>3328-1262-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3624.34</v>
+        <v>10497.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2069-4512-CM26</t>
+          <t>2069-4731-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3653.3</v>
+        <v>76139.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>812030-528-CM26</t>
+          <t>1549-2292-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4333.46</v>
+        <v>24082.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1549-2292-CM26</t>
+          <t>812030-528-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>24082.25</v>
+        <v>4333.46</v>
       </c>
     </row>
     <row r="27">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2649,7 +2649,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3328-1444-CM26</t>
+          <t>800-3466-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2727.89</v>
+        <v>2624.32</v>
       </c>
     </row>
     <row r="38">
@@ -2771,7 +2771,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057503-3007-CM26</t>
+          <t>3328-1444-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>30044.7</v>
+        <v>2727.89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>800-3466-CM26</t>
+          <t>1057503-3007-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2624.32</v>
+        <v>30044.7</v>
       </c>
     </row>
     <row r="41">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3991,7 +3991,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2111-10165-CM26</t>
+          <t>2111-10164-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4457.05</v>
+        <v>4288.39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2111-10164-CM26</t>
+          <t>2111-10165-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4288.39</v>
+        <v>4457.05</v>
       </c>
     </row>
     <row r="61">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2069-5912-CM26</t>
+          <t>2069-5517-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4357,7 +4357,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2069-5934-CM26</t>
+          <t>2069-5522-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3684.92</v>
+        <v>3784.76</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2069-5911-CM26</t>
+          <t>2069-5525-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5270.71</v>
+        <v>3513.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2069-5528-CM26</t>
+          <t>2069-5526-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5458.34</v>
+        <v>2346.16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2069-5908-CM26</t>
+          <t>2069-5528-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>12773.56</v>
+        <v>5458.34</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2069-5525-CM26</t>
+          <t>2069-5908-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3513.8</v>
+        <v>12773.56</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2069-5522-CM26</t>
+          <t>2069-5911-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3784.76</v>
+        <v>5270.71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2069-5517-CM26</t>
+          <t>2069-5912-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4784,7 +4784,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2069-5526-CM26</t>
+          <t>2069-5934-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2346.16</v>
+        <v>3684.92</v>
       </c>
     </row>
     <row r="73">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4906,7 +4906,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2069-5521-CM26</t>
+          <t>2069-6030-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>8091.56</v>
+        <v>7414.69</v>
       </c>
     </row>
     <row r="75">
@@ -5028,7 +5028,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2069-6030-CM26</t>
+          <t>2069-5521-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7414.69</v>
+        <v>8091.56</v>
       </c>
     </row>
     <row r="77">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5150,7 +5150,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2069-5913-CM26</t>
+          <t>1057049-15556-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8758.370000000001</v>
+        <v>6736.87</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1057489-8316-CM26</t>
+          <t>2069-5913-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>24408.11</v>
+        <v>8758.370000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1057049-15556-CM26</t>
+          <t>1057489-8316-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5292,17 +5292,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>6736.87</v>
+        <v>24408.11</v>
       </c>
     </row>
     <row r="81">
@@ -5455,7 +5455,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2069-6189-CM26</t>
+          <t>3378-6046-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>10863.72</v>
+        <v>4070.68</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2069-6191-CM26</t>
+          <t>2069-6352-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>7561.02</v>
+        <v>4085.13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1057503-3428-CM26</t>
+          <t>2069-6356-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5597,17 +5597,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>42919.12</v>
+        <v>13225.4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2069-6352-CM26</t>
+          <t>2069-6191-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4085.13</v>
+        <v>7561.02</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2069-6356-CM26</t>
+          <t>2069-6189-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>13225.4</v>
+        <v>10863.72</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3378-6046-CM26</t>
+          <t>1057503-3428-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5780,17 +5780,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4070.68</v>
+        <v>42919.12</v>
       </c>
     </row>
     <row r="89">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5943,7 +5943,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1057491-4167-CM26</t>
+          <t>1057882-9-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>12032.97</v>
+        <v>17570.04</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>812030-753-CM26</t>
+          <t>3378-6087-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4206.51</v>
+        <v>2702.72</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3378-6087-CM26</t>
+          <t>812030-753-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2702.72</v>
+        <v>4206.51</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057882-9-CM26</t>
+          <t>1057491-4167-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>17570.04</v>
+        <v>12032.97</v>
       </c>
     </row>
     <row r="95">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6370,7 +6370,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057501-7867-CM26</t>
+          <t>1057501-8128-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>57603.57</v>
+        <v>20743.53</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1057501-7870-CM26</t>
+          <t>812030-765-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>55218.01</v>
+        <v>10390.37</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1057501-7871-CM26</t>
+          <t>1057501-7870-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>27708.12</v>
+        <v>55218.01</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>812030-765-CM26</t>
+          <t>1057501-7871-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6573,17 +6573,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>10390.37</v>
+        <v>27708.12</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1057501-8128-CM26</t>
+          <t>1057501-7867-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>20743.53</v>
+        <v>57603.57</v>
       </c>
     </row>
     <row r="103">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7285,7 +7285,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2069-6748-CM26</t>
+          <t>2069-6759-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3500.77</v>
+        <v>3320.87</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2069-6712-CM26</t>
+          <t>2069-6748-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5335.07</v>
+        <v>3500.77</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2069-6759-CM26</t>
+          <t>2069-6712-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3320.87</v>
+        <v>5335.07</v>
       </c>
     </row>
     <row r="116">
@@ -7956,7 +7956,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2069-6762-CM26</t>
+          <t>2069-6959-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>5250.87</v>
+        <v>9601.57</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2069-6959-CM26</t>
+          <t>2069-6762-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>9601.57</v>
+        <v>5250.87</v>
       </c>
     </row>
     <row r="126">
@@ -8505,7 +8505,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1549-3603-CM26</t>
+          <t>2069-7311-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8525,17 +8525,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>68447.7</v>
+        <v>8498.540000000001</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2069-7311-CM26</t>
+          <t>1549-3603-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8586,17 +8586,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>8498.540000000001</v>
+        <v>68447.7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1549-3602-CM26</t>
+          <t>2111-11646-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8647,17 +8647,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>73577.87</v>
+        <v>2603.4</v>
       </c>
     </row>
     <row r="136">
@@ -8749,7 +8749,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2111-11646-CM26</t>
+          <t>1549-3602-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8769,17 +8769,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2603.4</v>
+        <v>73577.87</v>
       </c>
     </row>
     <row r="138">
@@ -9054,7 +9054,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1057501-9565-CM26</t>
+          <t>812030-890-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>46134.59</v>
+        <v>3722.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>812030-890-CM26</t>
+          <t>1549-3689-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9135,17 +9135,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>3722.5</v>
+        <v>56556.75</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1549-3689-CM26</t>
+          <t>1057501-9565-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9196,17 +9196,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>56556.75</v>
+        <v>46134.59</v>
       </c>
     </row>
     <row r="145">
@@ -9298,7 +9298,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>812030-798-CM26</t>
+          <t>1057049-17540-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5757.16</v>
+        <v>2358.69</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1641-19026-CM26</t>
+          <t>3378-7297-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9379,17 +9379,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.608.204-3</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>7581.93</v>
+        <v>3912.08</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1641-19028-CM26</t>
+          <t>3328-2156-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.608.204-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4717.64</v>
+        <v>14161.61</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1057049-17479-CM26</t>
+          <t>1641-19028-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3732.64</v>
+        <v>4717.64</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3328-2156-CM26</t>
+          <t>1057049-17479-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>14161.61</v>
+        <v>3732.64</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3378-7297-CM26</t>
+          <t>1641-19026-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9623,17 +9623,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3912.08</v>
+        <v>7581.93</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1057049-17540-CM26</t>
+          <t>812030-798-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2358.69</v>
+        <v>5757.16</v>
       </c>
     </row>
     <row r="153">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -10091,7 +10091,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1549-3800-CM26</t>
+          <t>3328-2237-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>75746.94</v>
+        <v>3504.09</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3328-2237-CM26</t>
+          <t>1549-3800-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10172,17 +10172,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3504.09</v>
+        <v>75746.94</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1549-3804-CM26</t>
+          <t>1549-3803-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>9764.559999999999</v>
+        <v>55550.71</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1549-3803-CM26</t>
+          <t>1549-3804-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>55550.71</v>
+        <v>9764.559999999999</v>
       </c>
     </row>
     <row r="163">
@@ -10391,6 +10391,2080 @@
       </c>
       <c r="M163" s="2" t="n">
         <v>7492.09</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2111-11983-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>2947.59</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2111-9761-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>6386.44</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2111-11588-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>20190.79</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2111-11996-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>3832.02</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1002772-9216-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>61.608.205-1</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>4104.9</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>538598-3123-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>61.979.450-8</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>4330.28</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1057501-10358-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>6626.54</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1549-3809-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>2599.64</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>3328-2294-CM26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>61.103.007-K</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>ARENYS MED S.A.</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>4460.17</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1549-4039-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>7237.75</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1057049-18220-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>74059.52</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>812030-917-CM26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>10301.25</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>3378-7927-CM26</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>61.101.030-3</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>2753.86</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1057491-5321-CM26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>61.608.408-9</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>NEUMANN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>78.936.310-2</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>5825.25</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1549-4107-CM26</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>73125.41</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1549-4099-CM26</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>10310.62</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1057049-17695-CM26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>6345.23</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1057501-10748-CM26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>38997.52</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1057501-10834-CM26</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>15194.46</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2111-12184-CM26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>3422.72</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2111-12249-CM26</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>2472.17</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2111-12471-CM26</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>3336.48</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2111-12494-CM26</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>2908.73</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1058078-3038-CM26</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>61.602.123-0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Hospital de Melipilla</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>8199.02</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1057049-18545-CM26</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>62230.66</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1057491-5473-CM26</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>61.608.408-9</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>NEUMANN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>78.936.310-2</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>5759.74</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>3328-2447-CM26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>61.103.007-K</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>5567.25</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1549-4205-CM26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>72274.78</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1058078-3123-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>61.602.123-0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Hospital de Melipilla</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>4566.73</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>812030-974-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>4383.67</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>812030-953-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>40858.64</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2109-1998-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>61.608.203-5</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>HARMONY MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>77.447.444-7</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>7246.98</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>812030-952-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>40018.36</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2109-2016-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.608.203-5</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>3004.25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
@@ -623,7 +623,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1908,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +1973,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3014,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3140,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5828,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +5954,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7056,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7182,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7735,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8288,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +8902,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9638,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +9825,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10073,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10565,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10691,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +10817,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +10882,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +10947,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11744,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +11809,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12423,11 @@
           <t>77.447.444-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M197"/>
+  <dimension ref="A1:M217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -688,7 +688,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -762,7 +766,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1549-2076-CM26</t>
+          <t>1549-2082-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -810,20 +814,24 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>33623.37</v>
+        <v>28351.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1549-2077-CM26</t>
+          <t>1549-2080-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -871,20 +879,24 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>15123.24</v>
+        <v>6761.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1549-2080-CM26</t>
+          <t>1549-2077-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -932,20 +944,24 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6761.2</v>
+        <v>15123.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1549-2081-CM26</t>
+          <t>1549-2076-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -993,20 +1009,24 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>56451.71</v>
+        <v>33623.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1549-2082-CM26</t>
+          <t>1549-2085-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1054,20 +1074,24 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>28351.28</v>
+        <v>5040.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1549-2085-CM26</t>
+          <t>3471-1634-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1087,17 +1111,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>60.505.723-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1131,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1146,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5040.29</v>
+        <v>7497.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3471-1634-CM26</t>
+          <t>1549-2081-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1148,17 +1172,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.505.723-3</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,22 +1192,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7497.75</v>
+        <v>56451.71</v>
       </c>
     </row>
     <row r="13">
@@ -1311,7 +1339,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2069-4231-CM26</t>
+          <t>2069-4326-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,13 +1394,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3597.72</v>
+        <v>7195.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2069-4233-CM26</t>
+          <t>2069-4234-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1433,7 +1461,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2069-4234-CM26</t>
+          <t>2069-4280-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1494,7 +1522,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2069-4280-CM26</t>
+          <t>3378-4411-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1519,12 +1547,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,28 +1562,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3597.72</v>
+        <v>6347.65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2069-4326-CM26</t>
+          <t>2069-4233-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1610,13 +1642,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>7195.44</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3378-4411-CM26</t>
+          <t>2069-4231-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1641,12 +1673,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1688,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,7 +1703,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6347.65</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="21">
@@ -1925,7 +1957,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1549-2292-CM26</t>
+          <t>812030-528-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1950,12 +1982,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1965,12 +1997,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1984,13 +2016,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>24082.25</v>
+        <v>4333.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>812030-528-CM26</t>
+          <t>1549-2292-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2015,12 +2047,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2030,22 +2062,26 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4333.46</v>
+        <v>24082.25</v>
       </c>
     </row>
     <row r="27">
@@ -2234,7 +2270,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>812030-622-CM26</t>
+          <t>3378-4788-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2254,17 +2290,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2274,28 +2310,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3006.57</v>
+        <v>63871.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3378-4788-CM26</t>
+          <t>812030-622-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2315,17 +2355,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2335,12 +2375,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2350,7 +2390,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>63871.9</v>
+        <v>3006.57</v>
       </c>
     </row>
     <row r="32">
@@ -2465,7 +2505,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2478,7 +2522,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3328-1342-CM26</t>
+          <t>3471-1979-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2498,17 +2542,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>60.505.723-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2533,13 +2577,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4079.07</v>
+        <v>4863.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3328-1369-CM26</t>
+          <t>3328-1342-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2594,13 +2638,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2603.65</v>
+        <v>4079.07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3471-1979-CM26</t>
+          <t>3328-1369-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2620,17 +2664,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.505.723-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2655,13 +2699,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4863.89</v>
+        <v>2603.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>800-3466-CM26</t>
+          <t>812030-659-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2681,17 +2725,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2709,20 +2753,24 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2624.32</v>
+        <v>4232.69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>812030-659-CM26</t>
+          <t>1057503-3007-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2747,12 +2795,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2770,14 +2818,18 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4232.69</v>
+        <v>30044.7</v>
       </c>
     </row>
     <row r="39">
@@ -2844,7 +2896,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057503-3007-CM26</t>
+          <t>800-3466-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2864,17 +2916,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2892,14 +2944,18 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>30044.7</v>
+        <v>2624.32</v>
       </c>
     </row>
     <row r="41">
@@ -2953,7 +3009,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2966,7 +3026,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1057501-5644-CM26</t>
+          <t>3328-1426-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2991,12 +3051,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3006,32 +3066,28 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2673.77</v>
+        <v>3262.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3328-1426-CM26</t>
+          <t>1947-2902-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3056,12 +3112,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.004-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3071,28 +3127,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3262.91</v>
+        <v>2566.82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1947-2902-CM26</t>
+          <t>812030-677-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3117,12 +3177,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.608.004-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3132,12 +3192,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3151,13 +3211,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2566.82</v>
+        <v>8061.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>812030-677-CM26</t>
+          <t>1057501-5644-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3182,12 +3242,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3197,22 +3257,26 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8061.89</v>
+        <v>2673.77</v>
       </c>
     </row>
     <row r="46">
@@ -3340,7 +3404,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1549-2709-CM26</t>
+          <t>1549-2703-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3388,20 +3452,24 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>28167.55</v>
+        <v>15025.23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1549-2707-CM26</t>
+          <t>1549-2697-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3449,14 +3517,18 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>14604.29</v>
+        <v>68775.98</v>
       </c>
     </row>
     <row r="50">
@@ -3510,7 +3582,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3523,7 +3599,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1549-2703-CM26</t>
+          <t>1549-2707-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3571,20 +3647,24 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>15025.23</v>
+        <v>14604.29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1549-2697-CM26</t>
+          <t>1549-2709-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3632,14 +3712,18 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>68775.98</v>
+        <v>28167.55</v>
       </c>
     </row>
     <row r="53">
@@ -3706,7 +3790,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2111-9985-CM26</t>
+          <t>812030-711-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3731,12 +3815,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3746,28 +3830,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>16518.53</v>
+        <v>6207.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>812030-711-CM26</t>
+          <t>2111-10040-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3792,12 +3880,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3807,12 +3895,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3822,13 +3910,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6207.48</v>
+        <v>4129.63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2111-10040-CM26</t>
+          <t>2111-9985-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3883,7 +3971,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4129.63</v>
+        <v>16518.53</v>
       </c>
     </row>
     <row r="57">
@@ -4011,7 +4099,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2111-10164-CM26</t>
+          <t>2111-10165-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4051,12 +4139,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4066,13 +4154,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4288.39</v>
+        <v>4457.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2111-10165-CM26</t>
+          <t>2111-10164-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4112,12 +4200,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4127,13 +4215,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4457.05</v>
+        <v>4288.39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>812030-712-CM26</t>
+          <t>1057489-8114-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4158,12 +4246,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4173,12 +4261,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4188,13 +4276,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>45337.65</v>
+        <v>5146.48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057489-8114-CM26</t>
+          <t>812030-712-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4219,12 +4307,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4234,12 +4322,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4249,7 +4337,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5146.48</v>
+        <v>45337.65</v>
       </c>
     </row>
     <row r="63">
@@ -4316,7 +4404,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2069-5517-CM26</t>
+          <t>2069-5911-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4371,13 +4459,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3491.07</v>
+        <v>5270.71</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2069-5522-CM26</t>
+          <t>2069-5908-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4432,13 +4520,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3784.76</v>
+        <v>12773.56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2069-5525-CM26</t>
+          <t>2069-5528-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4493,7 +4581,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3513.8</v>
+        <v>5458.34</v>
       </c>
     </row>
     <row r="67">
@@ -4560,7 +4648,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2069-5528-CM26</t>
+          <t>2069-5525-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4615,13 +4703,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5458.34</v>
+        <v>3513.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2069-5908-CM26</t>
+          <t>2069-5934-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4676,13 +4764,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>12773.56</v>
+        <v>3684.92</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2069-5911-CM26</t>
+          <t>2069-5517-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4737,7 +4825,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5270.71</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="71">
@@ -4804,7 +4892,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2069-5934-CM26</t>
+          <t>2069-5522-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4859,7 +4947,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3684.92</v>
+        <v>3784.76</v>
       </c>
     </row>
     <row r="73">
@@ -4926,7 +5014,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2069-6030-CM26</t>
+          <t>2069-6029-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4981,13 +5069,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>7414.69</v>
+        <v>3331.82</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2069-6029-CM26</t>
+          <t>2069-6030-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5042,7 +5130,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3331.82</v>
+        <v>7414.69</v>
       </c>
     </row>
     <row r="76">
@@ -5157,7 +5245,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5475,7 +5567,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3378-6046-CM26</t>
+          <t>2069-6191-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5500,12 +5592,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5530,13 +5622,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4070.68</v>
+        <v>7561.02</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2069-6352-CM26</t>
+          <t>1057503-3428-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5556,17 +5648,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5576,22 +5668,26 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4085.13</v>
+        <v>42919.12</v>
       </c>
     </row>
     <row r="85">
@@ -5658,7 +5754,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2069-6191-CM26</t>
+          <t>3378-6046-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5683,12 +5779,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5713,7 +5809,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7561.02</v>
+        <v>4070.68</v>
       </c>
     </row>
     <row r="87">
@@ -5780,7 +5876,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1057503-3428-CM26</t>
+          <t>2069-6352-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5800,17 +5896,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5820,26 +5916,22 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>42919.12</v>
+        <v>4085.13</v>
       </c>
     </row>
     <row r="89">
@@ -5971,7 +6063,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1057882-9-CM26</t>
+          <t>3378-6087-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5996,12 +6088,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6011,12 +6103,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6026,13 +6118,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>17570.04</v>
+        <v>2702.72</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3378-6087-CM26</t>
+          <t>812030-753-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6052,17 +6144,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6072,28 +6164,32 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2702.72</v>
+        <v>4206.51</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>812030-753-CM26</t>
+          <t>1057491-4167-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6113,17 +6209,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6133,12 +6229,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6148,13 +6244,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4206.51</v>
+        <v>12032.97</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057491-4167-CM26</t>
+          <t>1057882-9-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6179,12 +6275,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6194,12 +6290,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6209,7 +6305,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>12032.97</v>
+        <v>17570.04</v>
       </c>
     </row>
     <row r="95">
@@ -6263,7 +6359,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6276,7 +6376,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3328-1722-CM26</t>
+          <t>3328-1751-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6316,12 +6416,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6331,13 +6431,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4406.13</v>
+        <v>5448.74</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3328-1751-CM26</t>
+          <t>3328-1722-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6377,12 +6477,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6392,7 +6492,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5448.74</v>
+        <v>4406.13</v>
       </c>
     </row>
     <row r="98">
@@ -6507,7 +6607,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6520,7 +6624,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1057501-7870-CM26</t>
+          <t>1057501-7871-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6575,13 +6679,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>55218.01</v>
+        <v>27708.12</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1057501-7871-CM26</t>
+          <t>1057501-7870-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6636,7 +6740,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>27708.12</v>
+        <v>55218.01</v>
       </c>
     </row>
     <row r="102">
@@ -6764,7 +6868,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3328-1738-CM26</t>
+          <t>3378-6339-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6789,12 +6893,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6804,12 +6908,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6819,7 +6923,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>5557.72</v>
+        <v>2461.82</v>
       </c>
     </row>
     <row r="105">
@@ -6886,7 +6990,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3378-6339-CM26</t>
+          <t>3328-1738-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6911,12 +7015,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6926,12 +7030,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6941,7 +7045,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2461.82</v>
+        <v>5557.72</v>
       </c>
     </row>
     <row r="107">
@@ -7008,7 +7112,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1549-3291-CM26</t>
+          <t>812030-776-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7028,17 +7132,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7048,32 +7152,28 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3502.27</v>
+        <v>45364.17</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>812030-776-CM26</t>
+          <t>1549-3291-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7093,17 +7193,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7113,28 +7213,32 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>45364.17</v>
+        <v>3502.27</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3328-1937-CM26</t>
+          <t>2069-6712-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7159,12 +7263,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7174,32 +7278,28 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>20259.26</v>
+        <v>5335.07</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1549-3347-CM26</t>
+          <t>2069-6748-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7224,12 +7324,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7239,12 +7339,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7254,7 +7354,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>49721.66</v>
+        <v>3500.77</v>
       </c>
     </row>
     <row r="112">
@@ -7321,7 +7421,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2069-6759-CM26</t>
+          <t>1549-3347-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7346,12 +7446,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7361,28 +7461,32 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3320.87</v>
+        <v>49721.66</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2069-6748-CM26</t>
+          <t>3328-1937-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7407,12 +7511,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7422,28 +7526,32 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3500.77</v>
+        <v>20259.26</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2069-6712-CM26</t>
+          <t>2069-6759-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7498,7 +7606,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5335.07</v>
+        <v>3320.87</v>
       </c>
     </row>
     <row r="116">
@@ -7613,7 +7721,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7626,7 +7738,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1057049-17208-CM26</t>
+          <t>1057494-2969-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7646,17 +7758,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.102-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7666,28 +7778,32 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>66844.28999999999</v>
+        <v>3294.09</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1057494-2969-CM26</t>
+          <t>1057049-17208-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7707,17 +7823,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.608.102-0</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7727,26 +7843,22 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3294.09</v>
+        <v>66844.28999999999</v>
       </c>
     </row>
     <row r="120">
@@ -7800,7 +7912,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7874,7 +7990,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1057491-4650-CM26</t>
+          <t>2069-6703-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7894,17 +8010,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7914,12 +8030,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7929,13 +8045,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>12173.07</v>
+        <v>7478.62</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2069-6962-CM26</t>
+          <t>2069-6762-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7990,7 +8106,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5313.91</v>
+        <v>5250.87</v>
       </c>
     </row>
     <row r="124">
@@ -8057,7 +8173,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2069-6762-CM26</t>
+          <t>2069-6962-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8112,13 +8228,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>5250.87</v>
+        <v>5313.91</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2069-6703-CM26</t>
+          <t>1057491-4650-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8138,17 +8254,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8158,12 +8274,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8173,7 +8289,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>7478.62</v>
+        <v>12173.07</v>
       </c>
     </row>
     <row r="127">
@@ -8353,7 +8469,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8366,7 +8486,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>812030-824-CM26</t>
+          <t>1057491-4687-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8391,12 +8511,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8406,12 +8526,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8421,13 +8541,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>10599.79</v>
+        <v>6082.87</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1057491-4687-CM26</t>
+          <t>812030-824-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8452,12 +8572,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8467,22 +8587,26 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>6082.87</v>
+        <v>10599.79</v>
       </c>
     </row>
     <row r="132">
@@ -8549,7 +8673,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2069-7311-CM26</t>
+          <t>1549-3603-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8569,17 +8693,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8589,12 +8713,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8604,13 +8728,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>8498.540000000001</v>
+        <v>68447.7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1549-3603-CM26</t>
+          <t>2069-7311-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8630,17 +8754,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8650,12 +8774,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8665,13 +8789,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>68447.7</v>
+        <v>8498.540000000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2111-11646-CM26</t>
+          <t>1549-3602-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8691,17 +8815,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8711,28 +8835,32 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2603.4</v>
+        <v>73577.87</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2111-11638-CM26</t>
+          <t>2111-11646-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8787,13 +8915,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>4100.35</v>
+        <v>2603.4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1549-3602-CM26</t>
+          <t>2111-11638-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8813,17 +8941,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8833,12 +8961,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8848,7 +8976,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>73577.87</v>
+        <v>4100.35</v>
       </c>
     </row>
     <row r="138">
@@ -8919,7 +9047,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2069-7593-CM26</t>
+          <t>2069-7602-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8939,7 +9067,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8974,13 +9102,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>19069.59</v>
+        <v>7578.59</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2069-7595-CM26</t>
+          <t>2069-7593-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9035,13 +9163,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>14853.23</v>
+        <v>19069.59</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2069-7602-CM26</t>
+          <t>2069-7595-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9061,7 +9189,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9096,13 +9224,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>7578.59</v>
+        <v>14853.23</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>812030-890-CM26</t>
+          <t>1057501-9565-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9127,12 +9255,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9142,12 +9270,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9157,7 +9285,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3722.5</v>
+        <v>46134.59</v>
       </c>
     </row>
     <row r="143">
@@ -9224,7 +9352,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1057501-9565-CM26</t>
+          <t>812030-890-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9249,12 +9377,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9264,28 +9392,32 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>46134.59</v>
+        <v>3722.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2111-11754-CM26</t>
+          <t>1641-19026-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9305,17 +9437,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9325,12 +9457,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9340,13 +9472,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2621.92</v>
+        <v>7581.93</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1057049-17540-CM26</t>
+          <t>1641-19028-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9371,12 +9503,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9386,12 +9518,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9401,13 +9533,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2358.69</v>
+        <v>4717.64</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3378-7297-CM26</t>
+          <t>1057049-17540-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9427,17 +9559,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9447,12 +9579,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9462,13 +9594,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>3912.08</v>
+        <v>2358.69</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3328-2156-CM26</t>
+          <t>2111-11754-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9488,17 +9620,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9508,12 +9640,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9523,13 +9655,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>14161.61</v>
+        <v>2621.92</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1641-19028-CM26</t>
+          <t>3328-2156-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9554,12 +9686,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.608.204-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9569,12 +9701,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9584,7 +9716,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>4717.64</v>
+        <v>14161.61</v>
       </c>
     </row>
     <row r="150">
@@ -9655,7 +9787,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1641-19026-CM26</t>
+          <t>3378-7297-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9675,17 +9807,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.608.204-3</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9695,12 +9827,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9710,7 +9842,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>7581.93</v>
+        <v>3912.08</v>
       </c>
     </row>
     <row r="152">
@@ -10090,7 +10222,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1549-3801-CM26</t>
+          <t>1549-3800-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10130,12 +10262,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10145,7 +10277,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>69228.87</v>
+        <v>75746.94</v>
       </c>
     </row>
     <row r="159">
@@ -10212,7 +10344,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1549-3800-CM26</t>
+          <t>1549-3801-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10252,22 +10384,26 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>75746.94</v>
+        <v>69228.87</v>
       </c>
     </row>
     <row r="161">
@@ -10321,7 +10457,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10382,7 +10522,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10517,7 +10661,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2111-9761-CM26</t>
+          <t>2111-11996-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10557,12 +10701,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -10576,7 +10720,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>6386.44</v>
+        <v>3832.02</v>
       </c>
     </row>
     <row r="166">
@@ -10643,7 +10787,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2111-11996-CM26</t>
+          <t>2111-9761-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10683,12 +10827,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10702,7 +10846,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3832.02</v>
+        <v>6386.44</v>
       </c>
     </row>
     <row r="168">
@@ -10756,7 +10900,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10899,7 +11047,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1549-3809-CM26</t>
+          <t>3328-2294-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10919,17 +11067,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10939,32 +11087,28 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2599.64</v>
+        <v>4460.17</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3328-2294-CM26</t>
+          <t>1549-3809-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10984,17 +11128,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11004,28 +11148,32 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>4460.17</v>
+        <v>2599.64</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1549-4039-CM26</t>
+          <t>2111-12333-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11040,7 +11188,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11050,12 +11198,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11065,12 +11213,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11080,13 +11228,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>7237.75</v>
+        <v>10923.68</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1057049-18220-CM26</t>
+          <t>1549-4039-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11106,17 +11254,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11126,12 +11274,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11141,13 +11289,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>74059.52</v>
+        <v>7237.75</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>812030-917-CM26</t>
+          <t>1057049-18220-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11162,22 +11310,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11187,12 +11335,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11202,13 +11350,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>10301.25</v>
+        <v>74059.52</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3378-7927-CM26</t>
+          <t>812030-917-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11223,7 +11371,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11233,12 +11381,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11248,28 +11396,32 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2753.86</v>
+        <v>10301.25</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1057491-5321-CM26</t>
+          <t>3378-7927-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11284,7 +11436,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11294,12 +11446,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11309,12 +11461,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11324,13 +11476,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>5825.25</v>
+        <v>2753.86</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1549-4107-CM26</t>
+          <t>1057491-5321-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11345,7 +11497,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11355,12 +11507,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11370,12 +11522,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11385,13 +11537,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>73125.41</v>
+        <v>5825.25</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1549-4099-CM26</t>
+          <t>1549-4107-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11411,7 +11563,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11446,7 +11598,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>10310.62</v>
+        <v>73125.41</v>
       </c>
     </row>
     <row r="180">
@@ -11574,7 +11726,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1057501-10834-CM26</t>
+          <t>1549-4099-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11589,22 +11741,22 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11614,12 +11766,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11629,13 +11781,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>15194.46</v>
+        <v>10310.62</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2111-12184-CM26</t>
+          <t>1057501-10834-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11650,22 +11802,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11675,12 +11827,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11690,13 +11842,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3422.72</v>
+        <v>15194.46</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2111-12249-CM26</t>
+          <t>2111-12184-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11736,32 +11888,28 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2472.17</v>
+        <v>3422.72</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2111-12471-CM26</t>
+          <t>2111-12249-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11820,13 +11968,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3336.48</v>
+        <v>2472.17</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2111-12494-CM26</t>
+          <t>2111-12341-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11846,7 +11994,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11866,12 +12014,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11881,13 +12029,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2908.73</v>
+        <v>3585.59</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1058078-3038-CM26</t>
+          <t>2111-12471-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11907,17 +12055,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.602.123-0</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hospital de Melipilla</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11927,28 +12075,32 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>8199.02</v>
+        <v>3336.48</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1057049-18545-CM26</t>
+          <t>2111-12494-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11963,22 +12115,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11988,12 +12140,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -12003,13 +12155,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>62230.66</v>
+        <v>2908.73</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1057491-5473-CM26</t>
+          <t>1058078-3038-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12024,7 +12176,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12034,12 +12186,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.602.123-0</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12049,12 +12201,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -12064,13 +12216,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5759.74</v>
+        <v>8199.02</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3328-2447-CM26</t>
+          <t>1057049-18545-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12085,22 +12237,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12110,12 +12262,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12125,13 +12277,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>5567.25</v>
+        <v>62230.66</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1549-4205-CM26</t>
+          <t>1057491-5473-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12146,22 +12298,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12171,12 +12323,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12186,13 +12338,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>72274.78</v>
+        <v>5759.74</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1058078-3123-CM26</t>
+          <t>3328-2447-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12207,22 +12359,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.602.123-0</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hospital de Melipilla</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12247,7 +12399,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>4566.73</v>
+        <v>5567.25</v>
       </c>
     </row>
     <row r="193">
@@ -12301,7 +12453,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12314,7 +12470,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>812030-953-CM26</t>
+          <t>1549-4205-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12329,22 +12485,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12354,12 +12510,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12369,13 +12525,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>40858.64</v>
+        <v>72274.78</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2109-1998-CM26</t>
+          <t>1058078-3123-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12390,22 +12546,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.608.203-5</t>
+          <t>61.602.123-0</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12415,26 +12571,22 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>HARMONY MEDICAL SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>77.447.444-7</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>7246.98</v>
+        <v>4566.73</v>
       </c>
     </row>
     <row r="196">
@@ -12460,7 +12612,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -12501,7 +12653,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2109-2016-CM26</t>
+          <t>812030-953-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12521,17 +12673,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.608.203-5</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12541,12 +12693,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12556,7 +12708,1251 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
+        <v>40858.64</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2109-2016-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>61.608.203-5</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
         <v>3004.25</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2109-1998-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>61.608.203-5</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>HARMONY MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>77.447.444-7</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>7246.98</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1057501-11049-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>3515.28</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1057491-5667-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>61.608.408-9</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>NEUMANN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>78.936.310-2</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>5691.73</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>3328-2546-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>61.103.007-K</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>6371.61</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1057494-3977-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>61.608.102-0</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>2316.48</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1549-4364-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>65515.74</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1057492-3714-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>61.959.800-8</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>2954.91</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1057492-3748-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>61.959.800-8</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>5642.29</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1057492-3778-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>61.959.800-8</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>29245.05</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2111-13022-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>2981.13</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1057049-18804-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>HEMISFERIO SUR S.A.</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>6088.47</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>812030-938-CM26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>21454.28</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2111-13128-CM26</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="n">
+        <v>4498.37</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>3378-8711-CM26</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>61.101.030-3</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="n">
+        <v>2542.83</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>3378-8712-CM26</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>61.101.030-3</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="n">
+        <v>3851.69</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>3378-8713-CM26</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>61.101.030-3</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="n">
+        <v>3851.69</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2111-13124-CM26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>2276.71</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1057049-18978-CM26</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="n">
+        <v>11552.69</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1057501-12037-CM26</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>2518.1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M217"/>
+  <dimension ref="A1:M221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3378-5546-CM26</t>
+          <t>2111-10065-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3566.62</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2069-5911-CM26</t>
+          <t>3378-5546-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4459,13 +4459,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5270.71</v>
+        <v>3566.62</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2069-5908-CM26</t>
+          <t>2069-5526-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4520,13 +4520,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>12773.56</v>
+        <v>2346.16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2069-5528-CM26</t>
+          <t>2069-5525-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4581,13 +4581,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5458.34</v>
+        <v>3513.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2069-5526-CM26</t>
+          <t>2069-5522-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2346.16</v>
+        <v>3784.76</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2069-5525-CM26</t>
+          <t>2069-5517-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4703,13 +4703,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3513.8</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2069-5934-CM26</t>
+          <t>2111-9684-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4729,17 +4729,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3684.92</v>
+        <v>10907.42</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2069-5517-CM26</t>
+          <t>2069-5908-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4825,13 +4825,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3491.07</v>
+        <v>12773.56</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2069-5912-CM26</t>
+          <t>2069-5911-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3491.07</v>
+        <v>5270.71</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2069-5522-CM26</t>
+          <t>2069-5528-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4947,13 +4947,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3784.76</v>
+        <v>5458.34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3378-5622-CM26</t>
+          <t>2111-9619-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4968,22 +4968,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4102.21</v>
+        <v>3272.23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2069-6029-CM26</t>
+          <t>2069-5934-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5069,13 +5069,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3331.82</v>
+        <v>3684.92</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2069-6030-CM26</t>
+          <t>2111-10243-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5090,22 +5090,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5130,13 +5130,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7414.69</v>
+        <v>10907.42</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2069-5521-CM26</t>
+          <t>2069-5912-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5191,13 +5191,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8091.56</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>812030-704-CM26</t>
+          <t>3378-5622-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5237,32 +5237,28 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>10464.29</v>
+        <v>4102.21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1057049-15556-CM26</t>
+          <t>2069-5521-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5277,22 +5273,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5302,12 +5298,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5317,13 +5313,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>6736.87</v>
+        <v>8091.56</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2069-5913-CM26</t>
+          <t>2069-6029-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5338,7 +5334,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5378,13 +5374,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8758.370000000001</v>
+        <v>3331.82</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1057489-8316-CM26</t>
+          <t>2069-6030-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5399,7 +5395,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5409,12 +5405,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5424,12 +5420,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5439,13 +5435,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>24408.11</v>
+        <v>7414.69</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1057491-4113-CM26</t>
+          <t>812030-704-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5460,7 +5456,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5470,12 +5466,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5485,28 +5481,32 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>11974.81</v>
+        <v>10464.29</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1549-3011-CM26</t>
+          <t>2069-5913-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5521,22 +5521,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>67653.86</v>
+        <v>8758.370000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2069-6191-CM26</t>
+          <t>1057049-15556-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5582,22 +5582,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5622,13 +5622,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>7561.02</v>
+        <v>6736.87</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1057503-3428-CM26</t>
+          <t>1057489-8316-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5643,22 +5643,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5668,32 +5668,28 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>42919.12</v>
+        <v>24408.11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2069-6356-CM26</t>
+          <t>1057491-4113-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5708,7 +5704,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5718,12 +5714,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5733,12 +5729,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5748,13 +5744,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>13225.4</v>
+        <v>11974.81</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3378-6046-CM26</t>
+          <t>1549-3011-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5769,7 +5765,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5779,12 +5775,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5794,12 +5790,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5809,7 +5805,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4070.68</v>
+        <v>67653.86</v>
       </c>
     </row>
     <row r="87">
@@ -5876,7 +5872,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2069-6352-CM26</t>
+          <t>2069-6191-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5931,13 +5927,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4085.13</v>
+        <v>7561.02</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1057503-3492-CM26</t>
+          <t>1057503-3428-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5952,12 +5948,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5977,28 +5973,32 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>14816.35</v>
+        <v>42919.12</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057501-7822-CM26</t>
+          <t>2069-6352-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6013,22 +6013,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6038,32 +6038,28 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4117.74</v>
+        <v>4085.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3378-6087-CM26</t>
+          <t>2069-6356-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6078,7 +6074,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6088,12 +6084,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6103,12 +6099,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6118,13 +6114,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2702.72</v>
+        <v>13225.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>812030-753-CM26</t>
+          <t>3378-6046-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6139,22 +6135,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6164,32 +6160,28 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4206.51</v>
+        <v>4070.68</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1057491-4167-CM26</t>
+          <t>1057501-7822-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6204,7 +6196,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6214,12 +6206,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6229,28 +6221,32 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>12032.97</v>
+        <v>4117.74</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057882-9-CM26</t>
+          <t>1057503-3492-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6265,22 +6261,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6290,12 +6286,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6305,13 +6301,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>17570.04</v>
+        <v>14816.35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057501-7879-CM26</t>
+          <t>3378-6087-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6326,22 +6322,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6351,32 +6347,28 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>73393.87</v>
+        <v>2702.72</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3328-1751-CM26</t>
+          <t>812030-753-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6391,7 +6383,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6401,12 +6393,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6416,28 +6408,32 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5448.74</v>
+        <v>4206.51</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3328-1722-CM26</t>
+          <t>1057882-9-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6452,7 +6448,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6462,12 +6458,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6477,12 +6473,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6492,13 +6488,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4406.13</v>
+        <v>17570.04</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057501-8128-CM26</t>
+          <t>1057491-4167-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6513,22 +6509,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6538,12 +6534,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6553,13 +6549,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>20743.53</v>
+        <v>12032.97</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>812030-765-CM26</t>
+          <t>1057501-7879-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6574,7 +6570,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6584,12 +6580,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6618,13 +6614,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>10390.37</v>
+        <v>73393.87</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1057501-7871-CM26</t>
+          <t>3328-1751-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6639,7 +6635,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6649,12 +6645,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6679,13 +6675,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>27708.12</v>
+        <v>5448.74</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1057501-7870-CM26</t>
+          <t>3328-1722-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6700,7 +6696,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6710,12 +6706,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6725,12 +6721,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6740,7 +6736,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>55218.01</v>
+        <v>4406.13</v>
       </c>
     </row>
     <row r="102">
@@ -6807,7 +6803,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2111-10881-CM26</t>
+          <t>1057501-8128-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6822,22 +6818,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6847,12 +6843,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6862,13 +6858,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2640.98</v>
+        <v>20743.53</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3378-6339-CM26</t>
+          <t>812030-765-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6883,7 +6879,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6893,12 +6889,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6908,28 +6904,32 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2461.82</v>
+        <v>10390.37</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1549-3226-CM26</t>
+          <t>1057501-7871-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6944,22 +6944,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6984,13 +6984,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>67971.87</v>
+        <v>27708.12</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3328-1738-CM26</t>
+          <t>1057501-7870-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -7045,13 +7045,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5557.72</v>
+        <v>55218.01</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4776-382-CM26</t>
+          <t>2111-10881-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7066,22 +7066,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.108.000-k</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7091,12 +7091,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -7106,13 +7106,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2738.34</v>
+        <v>2640.98</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>812030-776-CM26</t>
+          <t>3378-6339-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7167,13 +7167,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>45364.17</v>
+        <v>2461.82</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1549-3291-CM26</t>
+          <t>1549-3226-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7213,32 +7213,28 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3502.27</v>
+        <v>67971.87</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2069-6712-CM26</t>
+          <t>3328-1738-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7253,22 +7249,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7278,12 +7274,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7293,13 +7289,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5335.07</v>
+        <v>5557.72</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2069-6748-CM26</t>
+          <t>4776-382-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7314,22 +7310,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.108.000-k</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7339,12 +7335,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7354,13 +7350,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3500.77</v>
+        <v>2738.34</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1057501-8311-CM26</t>
+          <t>1549-3291-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7375,7 +7371,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7385,12 +7381,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7400,28 +7396,32 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>6062.76</v>
+        <v>3502.27</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1549-3347-CM26</t>
+          <t>812030-776-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7436,22 +7436,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7461,32 +7461,28 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>49721.66</v>
+        <v>45364.17</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3328-1937-CM26</t>
+          <t>2069-6712-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7506,17 +7502,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7526,32 +7522,28 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>20259.26</v>
+        <v>5335.07</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2069-6759-CM26</t>
+          <t>2069-6748-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7571,7 +7563,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7606,13 +7598,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3320.87</v>
+        <v>3500.77</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1057049-17118-CM26</t>
+          <t>2069-6759-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7622,12 +7614,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7637,12 +7629,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7652,12 +7644,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7667,13 +7659,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2883.93</v>
+        <v>3320.87</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1057489-9198-CM26</t>
+          <t>1057501-8311-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7683,12 +7675,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7698,12 +7690,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7713,32 +7705,28 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3845.24</v>
+        <v>6062.76</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1057494-2969-CM26</t>
+          <t>1549-3347-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7748,12 +7736,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7763,12 +7751,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.608.102-0</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7778,12 +7766,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7797,13 +7785,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3294.09</v>
+        <v>49721.66</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1057049-17208-CM26</t>
+          <t>3328-1937-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7813,27 +7801,27 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7843,28 +7831,32 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>66844.28999999999</v>
+        <v>20259.26</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>800-4708-CM26</t>
+          <t>1057494-2969-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7879,22 +7871,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.102-0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7904,12 +7896,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>77.535.386-4</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7923,13 +7915,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3785.73</v>
+        <v>3294.09</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1057489-9314-CM26</t>
+          <t>1057489-9198-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7944,7 +7936,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7969,28 +7961,32 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>61473.81</v>
+        <v>3845.24</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2069-6703-CM26</t>
+          <t>1057049-17208-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8005,22 +8001,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8030,12 +8026,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -8045,13 +8041,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>7478.62</v>
+        <v>66844.28999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2069-6762-CM26</t>
+          <t>1057049-17118-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8066,22 +8062,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8091,12 +8087,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -8106,13 +8102,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5250.87</v>
+        <v>2883.93</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2069-6959-CM26</t>
+          <t>800-4708-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8127,7 +8123,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8137,12 +8133,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8152,28 +8148,32 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>9601.57</v>
+        <v>3785.73</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2069-6962-CM26</t>
+          <t>1057489-9314-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8188,22 +8188,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8228,13 +8228,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>5313.91</v>
+        <v>61473.81</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1057491-4650-CM26</t>
+          <t>2069-6703-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8289,13 +8289,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>12173.07</v>
+        <v>7478.62</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2069-6964-CM26</t>
+          <t>2069-6762-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8350,13 +8350,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>5446.38</v>
+        <v>5250.87</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1057501-8921-CM26</t>
+          <t>2069-6959-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8371,22 +8371,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8396,32 +8396,28 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5742.68</v>
+        <v>9601.57</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>812030-804-CM26</t>
+          <t>2069-6962-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8436,7 +8432,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8446,12 +8442,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8461,32 +8457,28 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>7690.35</v>
+        <v>5313.91</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1057491-4687-CM26</t>
+          <t>1057491-4650-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8501,7 +8493,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8541,13 +8533,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>6082.87</v>
+        <v>12173.07</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>812030-824-CM26</t>
+          <t>1057501-8921-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8562,22 +8554,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8587,12 +8579,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8606,13 +8598,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>10599.79</v>
+        <v>5742.68</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3378-6928-CM26</t>
+          <t>2069-6964-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8627,7 +8619,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8637,12 +8629,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8667,13 +8659,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>4145.84</v>
+        <v>5446.38</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1549-3603-CM26</t>
+          <t>812030-804-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8688,22 +8680,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8713,28 +8705,32 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>68447.7</v>
+        <v>7690.35</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2069-7311-CM26</t>
+          <t>1057491-4687-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8749,7 +8745,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8759,12 +8755,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8774,12 +8770,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8789,13 +8785,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>8498.540000000001</v>
+        <v>6082.87</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1549-3602-CM26</t>
+          <t>812030-824-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8810,7 +8806,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8820,12 +8816,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8854,13 +8850,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>73577.87</v>
+        <v>10599.79</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2111-11646-CM26</t>
+          <t>3378-6928-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8875,22 +8871,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8900,12 +8896,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8915,13 +8911,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2603.4</v>
+        <v>4145.84</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2111-11638-CM26</t>
+          <t>1549-3603-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8936,22 +8932,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8961,12 +8957,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8976,13 +8972,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4100.35</v>
+        <v>68447.7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1057049-17460-CM26</t>
+          <t>2069-7311-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8997,7 +8993,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9007,12 +9003,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9022,32 +9018,28 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>11343.41</v>
+        <v>8498.540000000001</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2069-7602-CM26</t>
+          <t>2111-11646-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9062,7 +9054,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9072,12 +9064,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9087,12 +9079,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -9102,13 +9094,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>7578.59</v>
+        <v>2603.4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2069-7593-CM26</t>
+          <t>2111-11638-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9123,22 +9115,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9148,12 +9140,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -9163,13 +9155,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>19069.59</v>
+        <v>4100.35</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2069-7595-CM26</t>
+          <t>1549-3602-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9184,7 +9176,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9194,12 +9186,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9209,28 +9201,32 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>14853.23</v>
+        <v>73577.87</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1057501-9565-CM26</t>
+          <t>1057049-17460-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9245,7 +9241,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9255,12 +9251,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9270,28 +9266,32 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr"/>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>46134.59</v>
+        <v>11343.41</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1549-3689-CM26</t>
+          <t>2069-7602-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9306,22 +9306,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>56556.75</v>
+        <v>7578.59</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>812030-890-CM26</t>
+          <t>2069-7593-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9392,32 +9392,28 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3722.5</v>
+        <v>19069.59</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1641-19026-CM26</t>
+          <t>2069-7595-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9432,22 +9428,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.608.204-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9457,12 +9453,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9472,13 +9468,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>7581.93</v>
+        <v>14853.23</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1641-19028-CM26</t>
+          <t>1057501-9565-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9493,22 +9489,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.608.204-3</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9518,12 +9514,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9533,13 +9529,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>4717.64</v>
+        <v>46134.59</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1057049-17540-CM26</t>
+          <t>1549-3689-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9554,22 +9550,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9579,12 +9575,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9594,13 +9590,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2358.69</v>
+        <v>56556.75</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2111-11754-CM26</t>
+          <t>812030-890-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9615,7 +9611,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9625,12 +9621,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9640,28 +9636,32 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2621.92</v>
+        <v>3722.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3328-2156-CM26</t>
+          <t>812030-798-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9681,17 +9681,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9716,13 +9716,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>14161.61</v>
+        <v>5757.16</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1057049-17479-CM26</t>
+          <t>1057049-17540-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9762,26 +9762,22 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3732.64</v>
+        <v>2358.69</v>
       </c>
     </row>
     <row r="151">
@@ -9848,7 +9844,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>812030-798-CM26</t>
+          <t>1641-19026-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9873,12 +9869,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9888,12 +9884,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9903,13 +9899,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>5757.16</v>
+        <v>7581.93</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1947-3865-CM26</t>
+          <t>1057049-17479-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9924,22 +9920,22 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.608.004-0</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9949,12 +9945,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9968,13 +9964,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2498.03</v>
+        <v>3732.64</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>812030-895-CM26</t>
+          <t>1641-19028-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9989,22 +9985,22 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10014,12 +10010,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -10029,13 +10025,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>59644.5</v>
+        <v>4717.64</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3378-7368-CM26</t>
+          <t>3328-2156-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10050,22 +10046,22 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10090,13 +10086,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3608.81</v>
+        <v>14161.61</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3328-2217-CM26</t>
+          <t>2111-11754-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10111,22 +10107,22 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10136,12 +10132,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -10151,13 +10147,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2779.07</v>
+        <v>2621.92</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3328-2227-CM26</t>
+          <t>1947-3865-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10172,7 +10168,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10182,12 +10178,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.004-0</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10197,12 +10193,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10216,13 +10212,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>8138.68</v>
+        <v>2498.03</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1549-3800-CM26</t>
+          <t>812030-895-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10237,7 +10233,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10247,12 +10243,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10262,12 +10258,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10277,13 +10273,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>75746.94</v>
+        <v>59644.5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3328-2237-CM26</t>
+          <t>3378-7368-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10298,7 +10294,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10308,12 +10304,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10323,12 +10319,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10338,13 +10334,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3504.09</v>
+        <v>3608.81</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1549-3801-CM26</t>
+          <t>3328-2217-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10359,22 +10355,22 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10384,32 +10380,28 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>69228.87</v>
+        <v>2779.07</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1549-3803-CM26</t>
+          <t>3328-2227-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10424,22 +10416,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10449,12 +10441,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>77.535.386-4</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10468,13 +10460,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>55550.71</v>
+        <v>8138.68</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1549-3804-CM26</t>
+          <t>1549-3800-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10489,12 +10481,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10514,32 +10506,28 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>9764.559999999999</v>
+        <v>75746.94</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2109-1794-CM26</t>
+          <t>3328-2237-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10554,7 +10542,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10564,12 +10552,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.608.203-5</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10579,12 +10567,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10594,13 +10582,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>7492.09</v>
+        <v>3504.09</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2111-11983-CM26</t>
+          <t>1549-3801-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10610,12 +10598,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10625,12 +10613,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10640,28 +10628,32 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2947.59</v>
+        <v>69228.87</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2111-11996-CM26</t>
+          <t>1549-3803-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10671,27 +10663,27 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10701,12 +10693,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -10720,13 +10712,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3832.02</v>
+        <v>55550.71</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2111-11588-CM26</t>
+          <t>1549-3804-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10736,27 +10728,27 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10766,28 +10758,32 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>20190.79</v>
+        <v>9764.559999999999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2111-9761-CM26</t>
+          <t>2109-1794-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10797,27 +10793,27 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.203-5</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10827,32 +10823,28 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>6386.44</v>
+        <v>7492.09</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1002772-9216-CM26</t>
+          <t>2111-11983-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10867,22 +10859,22 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.608.205-1</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10892,32 +10884,28 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4104.9</v>
+        <v>2947.59</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>538598-3123-CM26</t>
+          <t>2111-11996-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10932,22 +10920,22 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.979.450-8</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10957,12 +10945,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10976,13 +10964,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4330.28</v>
+        <v>3832.02</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1057501-10358-CM26</t>
+          <t>2111-11588-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10997,7 +10985,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11007,12 +10995,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11022,32 +11010,28 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6626.54</v>
+        <v>20190.79</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3328-2294-CM26</t>
+          <t>2111-9761-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11062,7 +11046,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -11072,12 +11056,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11087,28 +11071,32 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>4460.17</v>
+        <v>6386.44</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1549-3809-CM26</t>
+          <t>1002772-9216-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11123,22 +11111,22 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.205-1</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11148,12 +11136,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -11167,13 +11155,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2599.64</v>
+        <v>4104.9</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2111-12333-CM26</t>
+          <t>538598-3123-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11188,22 +11176,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.979.450-8</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11213,28 +11201,32 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>10923.68</v>
+        <v>4330.28</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1549-4039-CM26</t>
+          <t>1057501-10358-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11249,22 +11241,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11274,28 +11266,32 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>7237.75</v>
+        <v>6626.54</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1057049-18220-CM26</t>
+          <t>3328-2294-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11310,22 +11306,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11335,12 +11331,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11350,13 +11346,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>74059.52</v>
+        <v>4460.17</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>812030-917-CM26</t>
+          <t>1549-3809-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11371,7 +11367,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11381,12 +11377,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11396,12 +11392,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -11415,13 +11411,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>10301.25</v>
+        <v>2599.64</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3378-7927-CM26</t>
+          <t>2111-12333-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11436,22 +11432,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11461,12 +11457,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11476,13 +11472,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2753.86</v>
+        <v>10923.68</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1057491-5321-CM26</t>
+          <t>1549-4039-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11497,22 +11493,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11522,12 +11518,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11537,13 +11533,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5825.25</v>
+        <v>7237.75</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1549-4107-CM26</t>
+          <t>1057049-18220-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11558,7 +11554,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11568,12 +11564,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11598,13 +11594,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>73125.41</v>
+        <v>74059.52</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1057049-17695-CM26</t>
+          <t>812030-917-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11619,7 +11615,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11629,12 +11625,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11644,28 +11640,32 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>6345.23</v>
+        <v>10301.25</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1057501-10748-CM26</t>
+          <t>3378-7927-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11690,12 +11690,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11720,13 +11720,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>38997.52</v>
+        <v>2753.86</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1549-4099-CM26</t>
+          <t>1057491-5321-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11741,22 +11741,22 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11781,13 +11781,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>10310.62</v>
+        <v>5825.25</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1057501-10834-CM26</t>
+          <t>1549-4107-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11812,12 +11812,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11842,13 +11842,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>15194.46</v>
+        <v>73125.41</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2111-12184-CM26</t>
+          <t>1057049-17695-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11863,22 +11863,22 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11903,13 +11903,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3422.72</v>
+        <v>6345.23</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2111-12249-CM26</t>
+          <t>1057501-10748-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11924,22 +11924,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11949,32 +11949,28 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2472.17</v>
+        <v>38997.52</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2111-12341-CM26</t>
+          <t>1549-4099-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11989,7 +11985,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11999,12 +11995,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12014,12 +12010,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -12029,13 +12025,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3585.59</v>
+        <v>10310.62</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2111-12471-CM26</t>
+          <t>1057501-10834-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12050,22 +12046,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12075,32 +12071,28 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>3336.48</v>
+        <v>15194.46</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2111-12494-CM26</t>
+          <t>2111-12184-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12120,7 +12112,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -12140,12 +12132,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -12155,13 +12147,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2908.73</v>
+        <v>3422.72</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1058078-3038-CM26</t>
+          <t>2111-12249-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12181,17 +12173,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.602.123-0</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hospital de Melipilla</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12201,28 +12193,32 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8199.02</v>
+        <v>2472.17</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1057049-18545-CM26</t>
+          <t>2111-12341-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12237,22 +12233,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12262,12 +12258,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12277,13 +12273,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>62230.66</v>
+        <v>3585.59</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1057491-5473-CM26</t>
+          <t>2111-12471-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12298,22 +12294,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12323,28 +12319,32 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>5759.74</v>
+        <v>3336.48</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3328-2447-CM26</t>
+          <t>2111-12494-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12359,22 +12359,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12384,12 +12384,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12399,13 +12399,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>5567.25</v>
+        <v>2908.73</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>812030-974-CM26</t>
+          <t>1058078-3038-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12420,22 +12420,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.123-0</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12445,32 +12445,28 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>4383.67</v>
+        <v>8199.02</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1549-4205-CM26</t>
+          <t>1057049-18545-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12485,7 +12481,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12495,12 +12491,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12510,12 +12506,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12525,13 +12521,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>72274.78</v>
+        <v>62230.66</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1058078-3123-CM26</t>
+          <t>1057491-5473-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12546,7 +12542,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12556,12 +12552,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.602.123-0</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hospital de Melipilla</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12571,12 +12567,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12586,13 +12582,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>4566.73</v>
+        <v>5759.74</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>812030-952-CM26</t>
+          <t>3328-2447-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12607,22 +12603,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12647,13 +12643,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>40018.36</v>
+        <v>5567.25</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>812030-953-CM26</t>
+          <t>812030-974-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12668,12 +12664,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12693,28 +12689,32 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>40858.64</v>
+        <v>4383.67</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2109-2016-CM26</t>
+          <t>1549-4205-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.608.203-5</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3004.25</v>
+        <v>72274.78</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2109-1998-CM26</t>
+          <t>1058078-3123-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.608.203-5</t>
+          <t>61.602.123-0</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12815,32 +12815,28 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>HARMONY MEDICAL SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.447.444-7</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>7246.98</v>
+        <v>4566.73</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1057501-11049-CM26</t>
+          <t>812030-952-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12850,12 +12846,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12865,12 +12861,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12880,12 +12876,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12895,13 +12891,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3515.28</v>
+        <v>40018.36</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1057491-5667-CM26</t>
+          <t>812030-953-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12911,12 +12907,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12926,12 +12922,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12941,12 +12937,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12956,13 +12952,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>5691.73</v>
+        <v>40858.64</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3328-2546-CM26</t>
+          <t>2109-2016-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12972,27 +12968,27 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.203-5</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13002,12 +12998,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -13017,13 +13013,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>6371.61</v>
+        <v>3004.25</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1057494-3977-CM26</t>
+          <t>2109-1998-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13033,27 +13029,27 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.608.102-0</t>
+          <t>61.608.203-5</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13063,28 +13059,32 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>HARMONY MEDICAL SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr"/>
+          <t>77.447.444-7</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2316.48</v>
+        <v>7246.98</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1549-4364-CM26</t>
+          <t>1057501-11049-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13099,22 +13099,22 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13124,12 +13124,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -13139,13 +13139,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>65515.74</v>
+        <v>3515.28</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1057492-3714-CM26</t>
+          <t>1057491-5667-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13160,22 +13160,22 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13185,32 +13185,28 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.936.310-2</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2954.91</v>
+        <v>5691.73</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1057492-3748-CM26</t>
+          <t>3328-2546-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13225,7 +13221,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13235,12 +13231,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13250,32 +13246,28 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>5642.29</v>
+        <v>6371.61</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1057492-3778-CM26</t>
+          <t>1057494-3977-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13290,7 +13282,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13300,12 +13292,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.608.102-0</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13315,32 +13307,28 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>29245.05</v>
+        <v>2316.48</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2111-13022-CM26</t>
+          <t>1549-4364-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13355,7 +13343,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13365,12 +13353,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13380,12 +13368,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13395,13 +13383,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2981.13</v>
+        <v>65515.74</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1057049-18804-CM26</t>
+          <t>1057492-3714-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13416,22 +13404,22 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13441,28 +13429,32 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>6088.47</v>
+        <v>2954.91</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>812030-938-CM26</t>
+          <t>1057492-3748-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13477,7 +13469,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13487,12 +13479,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13502,28 +13494,32 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>21454.28</v>
+        <v>5642.29</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2111-13128-CM26</t>
+          <t>1057492-3778-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13538,7 +13534,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13548,12 +13544,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13563,12 +13559,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -13582,13 +13578,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>4498.37</v>
+        <v>29245.05</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3378-8711-CM26</t>
+          <t>2111-13022-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13603,22 +13599,22 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13643,13 +13639,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2542.83</v>
+        <v>2981.13</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3378-8712-CM26</t>
+          <t>1057049-18804-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13664,7 +13660,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13674,12 +13670,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13689,12 +13685,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13704,13 +13700,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3851.69</v>
+        <v>6088.47</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3378-8713-CM26</t>
+          <t>812030-938-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13725,22 +13721,22 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13750,12 +13746,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13765,13 +13761,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3851.69</v>
+        <v>21454.28</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2111-13124-CM26</t>
+          <t>2111-13128-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13786,12 +13782,12 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -13811,28 +13807,32 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2276.71</v>
+        <v>4498.37</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1057049-18978-CM26</t>
+          <t>3378-8711-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13847,22 +13847,22 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13872,12 +13872,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13887,71 +13887,315 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>11552.69</v>
+        <v>2542.83</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
+          <t>3378-8712-CM26</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>61.101.030-3</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>3851.69</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>3378-8713-CM26</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>61.101.030-3</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="n">
+        <v>3851.69</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2111-13124-CM26</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>61.608.602-2</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="n">
+        <v>2276.71</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1057049-18978-CM26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="n">
+        <v>11552.69</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
           <t>1057501-12037-CM26</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>61.608.502-6</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G221" t="inlineStr">
         <is>
           <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
         <is>
           <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr">
+      <c r="J221" t="inlineStr">
         <is>
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M217" s="2" t="n">
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="n">
         <v>2518.1</v>
       </c>
     </row>
